--- a/Design Files/Main-Board-v1.0/BOM/Client-BOM-Main Board - v1.0.xlsx
+++ b/Design Files/Main-Board-v1.0/BOM/Client-BOM-Main Board - v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="125">
   <si>
     <t>#</t>
   </si>
@@ -117,7 +117,7 @@
     <t>R3</t>
   </si>
   <si>
-    <t>R4, R5, R6, R8, R9, R10</t>
+    <t>R4, R5, R6, R8, R9, R10, R12</t>
   </si>
   <si>
     <t>R7, R11</t>
@@ -394,9 +394,6 @@
   </si>
   <si>
     <t>Custom</t>
-  </si>
-  <si>
-    <t>USB Connector</t>
   </si>
 </sst>
 </file>
@@ -894,10 +891,10 @@
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -1174,14 +1171,14 @@
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>25</v>
@@ -1221,7 +1218,7 @@
       <c r="E11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>124</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -1253,7 +1250,7 @@
       <c r="E12" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>124</v>
       </c>
       <c r="G12" s="10" t="s">
@@ -1285,7 +1282,7 @@
       <c r="E13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>124</v>
       </c>
       <c r="G13" s="8" t="s">
@@ -1426,7 +1423,7 @@
         <v>117</v>
       </c>
       <c r="J17" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17" s="7"/>
     </row>
@@ -1477,7 +1474,7 @@
       <c r="E19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>124</v>
       </c>
       <c r="G19" s="8" t="s">

--- a/Design Files/Main-Board-v1.0/BOM/Client-BOM-Main Board - v1.0.xlsx
+++ b/Design Files/Main-Board-v1.0/BOM/Client-BOM-Main Board - v1.0.xlsx
@@ -165,9 +165,6 @@
     <t>1x3P 3P PicoBlade(MX 1.25) Tin 3 -25℃~+85℃ 2A 1 1.25mm Brass Standing paste SMD,P=1.25mm Wire To Board Connector ROHS</t>
   </si>
   <si>
-    <t>CONN HEADER SMD R/A 4POS 1MM</t>
-  </si>
-  <si>
     <t>CONN HEADER SMD R/A 3POS 1MM</t>
   </si>
   <si>
@@ -225,9 +222,6 @@
     <t>HC-1.25-3PLT</t>
   </si>
   <si>
-    <t>SM04B-SRSS-TB(LF)(SN)</t>
-  </si>
-  <si>
     <t>SM03B-SRSS-TB(LF)(SN)</t>
   </si>
   <si>
@@ -394,6 +388,12 @@
   </si>
   <si>
     <t>Custom</t>
+  </si>
+  <si>
+    <t>1x4P 4P 1 SH 1mm Tin 4 -25℃~+85℃ Brass 1A Horizontal attachment SMD,P=1mm,Surface Mount，Right Angle Wire To Board Connector ROHS</t>
+  </si>
+  <si>
+    <t>ZX-SH1.0-4PWT</t>
   </si>
 </sst>
 </file>
@@ -929,22 +929,22 @@
         <v>39</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -963,16 +963,16 @@
         <v>40</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
@@ -995,16 +995,16 @@
         <v>41</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J4" s="9">
         <v>7</v>
@@ -1027,16 +1027,16 @@
         <v>42</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -1059,16 +1059,16 @@
         <v>43</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -1091,16 +1091,16 @@
         <v>44</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
@@ -1123,16 +1123,16 @@
         <v>45</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J8" s="9">
         <v>3</v>
@@ -1155,16 +1155,16 @@
         <v>46</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J9" s="7">
         <v>2</v>
@@ -1187,16 +1187,16 @@
         <v>6</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -1219,23 +1219,23 @@
         <v>47</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
       </c>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -1248,19 +1248,19 @@
         <v>27</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="H12" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>123</v>
+        <v>102</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -1280,19 +1280,19 @@
         <v>28</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J13" s="7">
         <v>1</v>
@@ -1312,19 +1312,19 @@
         <v>29</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J14" s="9">
         <v>2</v>
@@ -1344,19 +1344,19 @@
         <v>30</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J15" s="7">
         <v>2</v>
@@ -1376,19 +1376,19 @@
         <v>31</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -1408,19 +1408,19 @@
         <v>32</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J17" s="7">
         <v>7</v>
@@ -1440,19 +1440,19 @@
         <v>33</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J18" s="9">
         <v>2</v>
@@ -1472,19 +1472,19 @@
         <v>34</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J19" s="7">
         <v>2</v>
@@ -1504,19 +1504,19 @@
         <v>35</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
@@ -1536,19 +1536,19 @@
         <v>36</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -1568,19 +1568,19 @@
         <v>37</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J22" s="9">
         <v>1</v>
@@ -1600,19 +1600,19 @@
         <v>38</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J23" s="7">
         <v>1</v>
